--- a/supabase/Banco de Dados - venda-imoveis-caixa.xlsx
+++ b/supabase/Banco de Dados - venda-imoveis-caixa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PICHAU\Desktop\antigravity\venda-imoveis-caixa\supabase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDD6498-3EB6-493B-9E55-22E0AB2C3020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C8102F-227B-46A8-A692-D6DC4CBC267C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1275" yWindow="1950" windowWidth="13665" windowHeight="11295" xr2:uid="{CD85E196-7581-408E-B73E-D38E1D3215FC}"/>
   </bookViews>
